--- a/Simulation/Results/p.rand_Censor.Ints_mean.surv.10.xlsx
+++ b/Simulation/Results/p.rand_Censor.Ints_mean.surv.10.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">rand</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1 mins</t>
+    <t xml:space="preserve">5.8 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0692</v>
+        <v>0.0405</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0713</v>
+        <v>0.0428</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0659</v>
+        <v>0.0431</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0535</v>
+        <v>0.0431</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0635</v>
+        <v>0.0454</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0597</v>
+        <v>0.049</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0547</v>
+        <v>0.0459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0601</v>
+        <v>0.0467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0592</v>
+        <v>0.047</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0531</v>
+        <v>0.0493</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0557</v>
+        <v>0.048</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0524</v>
+        <v>0.0486</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
